--- a/testData/E2E_UAT_003_Part_2.xlsx
+++ b/testData/E2E_UAT_003_Part_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation_Project\E2E_Automation\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netapp-my.sharepoint.com/personal/sunilr2_netapp_com/Documents/Desktop/Playwright Python/E2E_Automation/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801E99C2-35A0-4437-9C2B-1ED0AF35F256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{801E99C2-35A0-4437-9C2B-1ED0AF35F256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4368A675-9448-4919-9111-ED92E46E4FE6}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>Test for Automation</t>
   </si>
   <si>
-    <t>To be Determined Before Qualify Sales Stage</t>
-  </si>
-  <si>
     <t>Direct</t>
   </si>
   <si>
@@ -238,6 +235,9 @@
   </si>
   <si>
     <t>CONFIGURE KEYSTONE PRODUCT</t>
+  </si>
+  <si>
+    <t>To be Determined at Qualify Sales Stage</t>
   </si>
 </sst>
 </file>
@@ -729,7 +729,7 @@
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -750,7 +750,7 @@
       <c r="R1" s="9"/>
       <c r="S1" s="9"/>
       <c r="T1" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U1" s="15"/>
       <c r="V1" s="15"/>
@@ -771,7 +771,7 @@
       <c r="AK1" s="15"/>
       <c r="AL1" s="16"/>
       <c r="AM1" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.4">
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -797,11 +797,11 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
       <c r="R2" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S2" s="10"/>
       <c r="T2" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U2" s="12"/>
       <c r="V2" s="12"/>
@@ -809,7 +809,7 @@
       <c r="X2" s="12"/>
       <c r="Y2" s="13"/>
       <c r="Z2" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA2" s="10"/>
       <c r="AB2" s="10"/>
@@ -817,18 +817,18 @@
       <c r="AD2" s="10"/>
       <c r="AE2" s="10"/>
       <c r="AF2" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AG2" s="10"/>
       <c r="AH2" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AI2" s="10"/>
       <c r="AJ2" s="10"/>
       <c r="AK2" s="10"/>
       <c r="AL2" s="10"/>
       <c r="AM2" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.4">
@@ -884,70 +884,70 @@
         <v>18</v>
       </c>
       <c r="R3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="T3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Y3" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="Z3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AF3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AG3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AH3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AI3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AJ3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AJ3" s="1" t="s">
+      <c r="AK3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AK3" s="1" t="s">
+      <c r="AL3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AL3" s="1" t="s">
+      <c r="AM3" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="AM3" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.4">
@@ -964,23 +964,23 @@
         <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -989,64 +989,64 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S4" s="4">
         <v>1000</v>
       </c>
       <c r="T4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="X4" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="Y4" s="4">
         <v>500</v>
       </c>
       <c r="Z4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AA4" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="AB4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AC4" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="AD4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AF4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AF4" s="3" t="s">
+      <c r="AG4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="AG4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH4" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="AI4" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
       <c r="AM4" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
